--- a/tests/fixtures/lom/1007922-1-LOM.xlsx
+++ b/tests/fixtures/lom/1007922-1-LOM.xlsx
@@ -14,35 +14,25 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>ITEM</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>PART NO</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>ITEM</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>PART NO</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
@@ -56,32 +46,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21897-1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1007922-1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PLATE A</t>
+          <t>TUBE</t>
         </is>
       </c>
     </row>
@@ -93,32 +73,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14149-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1007922-2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>PLATE B</t>
+          <t>FILLER</t>
         </is>
       </c>
     </row>
@@ -130,32 +100,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10099-1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1007922-3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PLATE C</t>
+          <t>TUBE</t>
         </is>
       </c>
     </row>
@@ -167,32 +127,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21750-1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1007922-4</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PLATE D</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
@@ -204,32 +154,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21743-1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1007922-5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PLATE E</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
@@ -241,32 +181,103 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1007830-1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1007922-6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PLATE F</t>
+          <t>OUTRIGGER LEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21750-2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21743-2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>73207</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ADDED CONFIGURATION</t>
         </is>
       </c>
     </row>
@@ -302,7 +313,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -312,19 +323,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1007922-1</t>
+          <t>21897-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PLATE A</t>
+          <t>TUBE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -334,19 +345,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1007922-2</t>
+          <t>14149-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PLATE B</t>
+          <t>FILLER</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -356,19 +367,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1007922-3</t>
+          <t>10099-1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLATE C</t>
+          <t>TUBE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -378,19 +389,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1007922-4</t>
+          <t>21750-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PLATE D</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -400,19 +411,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1007922-5</t>
+          <t>21743-1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PLATE E</t>
+          <t>PLATE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -422,12 +433,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1007922-6</t>
+          <t>1007830-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PLATE F</t>
+          <t>OUTRIGGER LEG</t>
         </is>
       </c>
     </row>
